--- a/medicinas.xlsx
+++ b/medicinas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Downloads\SERIES-DEL-TIEMPO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7C9D6D67-A8A5-444B-BEC8-4497CA998AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{AAE096B3-B22A-4279-8442-1373B424A43F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF558EFD-AF54-47B0-BA24-D4ACBF9F143C}"/>
   </bookViews>
